--- a/reports/Debug-purgatory-20260104/For Winter Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260104/For Winter Ending (Actual)_Visits.xlsx
@@ -434,10 +434,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>45974</v>
+        <v>45986</v>
       </c>
       <c r="C2" s="2">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,13 +448,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45983</v>
+        <v>45989</v>
       </c>
       <c r="C3" s="2">
-        <v>24</v>
+        <v>174</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -462,13 +462,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>45990</v>
+        <v>45989</v>
       </c>
       <c r="C4" s="2">
-        <v>239</v>
+        <v>95</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,10 +476,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45992</v>
+        <v>45990</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>7</v>
@@ -490,13 +490,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45993</v>
+        <v>45992</v>
       </c>
       <c r="C6" s="2">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="C7" s="2">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,13 +518,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>45999</v>
+        <v>45993</v>
       </c>
       <c r="C8" s="2">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,13 +532,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>46000</v>
+        <v>45994</v>
       </c>
       <c r="C9" s="2">
-        <v>322</v>
+        <v>63</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,13 +546,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46002</v>
+        <v>45995</v>
       </c>
       <c r="C10" s="2">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46003</v>
+        <v>45996</v>
       </c>
       <c r="C11" s="2">
-        <v>538</v>
+        <v>411</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>7</v>
@@ -574,10 +574,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>46004</v>
+        <v>45996</v>
       </c>
       <c r="C12" s="2">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>7</v>
@@ -588,13 +588,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>46005</v>
+        <v>45997</v>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>246</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,10 +602,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C14" s="2">
-        <v>13</v>
+        <v>358</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>7</v>
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>46006</v>
+        <v>45999</v>
       </c>
       <c r="C15" s="2">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,13 +630,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C16" s="2">
-        <v>382</v>
+        <v>133</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,10 +644,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C17" s="2">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>7</v>
@@ -658,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C18" s="2">
-        <v>1</v>
+        <v>212</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>46008</v>
+        <v>46004</v>
       </c>
       <c r="C19" s="2">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>7</v>
@@ -686,13 +686,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C20" s="2">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="C21" s="2">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>7</v>
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>46012</v>
+        <v>46011</v>
       </c>
       <c r="C22" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -728,13 +728,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>46012</v>
+        <v>46011</v>
       </c>
       <c r="C23" s="2">
-        <v>285</v>
+        <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +742,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>46013</v>
+        <v>46012</v>
       </c>
       <c r="C24" s="2">
-        <v>75</v>
+        <v>349</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>46015</v>
+        <v>46014</v>
       </c>
       <c r="C25" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>7</v>
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>46015</v>
+        <v>46014</v>
       </c>
       <c r="C26" s="2">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46017</v>
+        <v>46015</v>
       </c>
       <c r="C27" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>7</v>
@@ -798,13 +798,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>46018</v>
+        <v>46015</v>
       </c>
       <c r="C28" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>46018</v>
+        <v>46015</v>
       </c>
       <c r="C29" s="2">
-        <v>3</v>
+        <v>311</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>46019</v>
+        <v>46016</v>
       </c>
       <c r="C30" s="2">
-        <v>201</v>
+        <v>45</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,10 +840,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>46021</v>
+        <v>46017</v>
       </c>
       <c r="C31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>7</v>
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>46021</v>
+        <v>46017</v>
       </c>
       <c r="C32" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>7</v>
@@ -868,13 +868,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>46022</v>
+        <v>46017</v>
       </c>
       <c r="C33" s="2">
-        <v>493</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>46022</v>
+        <v>46018</v>
       </c>
       <c r="C34" s="2">
-        <v>2030</v>
+        <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>46023</v>
+        <v>46018</v>
       </c>
       <c r="C35" s="2">
-        <v>1</v>
+        <v>273</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,10 +910,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>46024</v>
+        <v>46019</v>
       </c>
       <c r="C36" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>7</v>
@@ -924,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>46024</v>
+        <v>46019</v>
       </c>
       <c r="C37" s="2">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>7</v>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>46025</v>
+        <v>46019</v>
       </c>
       <c r="C38" s="2">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>7</v>
@@ -952,13 +952,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>46025</v>
+        <v>46020</v>
       </c>
       <c r="C39" s="2">
-        <v>310</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>46025</v>
+        <v>46020</v>
       </c>
       <c r="C40" s="2">
-        <v>1100</v>
+        <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45984</v>
+        <v>46021</v>
       </c>
       <c r="C41" s="2">
-        <v>45</v>
+        <v>417</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +994,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45987</v>
+        <v>46021</v>
       </c>
       <c r="C42" s="2">
-        <v>46</v>
+        <v>696</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,10 +1008,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c r="C43" s="2">
-        <v>335</v>
+        <v>63</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>7</v>
@@ -1022,13 +1022,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45990</v>
+        <v>46022</v>
       </c>
       <c r="C44" s="2">
-        <v>164</v>
+        <v>40</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>45991</v>
+        <v>46023</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -1050,13 +1050,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45998</v>
+        <v>46024</v>
       </c>
       <c r="C46" s="2">
-        <v>4</v>
+        <v>608</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,13 +1064,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45998</v>
+        <v>46024</v>
       </c>
       <c r="C47" s="2">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46000</v>
+        <v>46025</v>
       </c>
       <c r="C48" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>7</v>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>46001</v>
+        <v>46025</v>
       </c>
       <c r="C49" s="2">
-        <v>1</v>
+        <v>1469</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>7</v>
@@ -1106,10 +1106,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>46001</v>
+        <v>46025</v>
       </c>
       <c r="C50" s="2">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>7</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>46002</v>
+        <v>46026</v>
       </c>
       <c r="C51" s="2">
-        <v>45</v>
+        <v>906</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,10 +1134,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>46003</v>
+        <v>46026</v>
       </c>
       <c r="C52" s="2">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>7</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>46003</v>
+        <v>46026</v>
       </c>
       <c r="C53" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>7</v>
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>46004</v>
+        <v>45966</v>
       </c>
       <c r="C54" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1176,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>46005</v>
+        <v>45969</v>
       </c>
       <c r="C55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,13 +1190,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>46005</v>
+        <v>45985</v>
       </c>
       <c r="C56" s="2">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>46005</v>
+        <v>45988</v>
       </c>
       <c r="C57" s="2">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,13 +1218,13 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>46006</v>
+        <v>45991</v>
       </c>
       <c r="C58" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>46006</v>
+        <v>45994</v>
       </c>
       <c r="C59" s="2">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>7</v>
@@ -1246,13 +1246,13 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>46008</v>
+        <v>45996</v>
       </c>
       <c r="C60" s="2">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>46009</v>
+        <v>45997</v>
       </c>
       <c r="C61" s="2">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>7</v>
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>46009</v>
+        <v>45997</v>
       </c>
       <c r="C62" s="2">
-        <v>345</v>
+        <v>14</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>7</v>
@@ -1288,13 +1288,13 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>46009</v>
+        <v>45998</v>
       </c>
       <c r="C63" s="2">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,13 +1302,13 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>46010</v>
+        <v>45998</v>
       </c>
       <c r="C64" s="2">
-        <v>533</v>
+        <v>34</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>46011</v>
+        <v>45999</v>
       </c>
       <c r="C65" s="2">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,13 +1330,13 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>46012</v>
+        <v>46001</v>
       </c>
       <c r="C66" s="2">
-        <v>883</v>
+        <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>46012</v>
+        <v>46002</v>
       </c>
       <c r="C67" s="2">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>7</v>
@@ -1358,13 +1358,13 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>46013</v>
+        <v>46004</v>
       </c>
       <c r="C68" s="2">
-        <v>1279</v>
+        <v>2</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,13 +1372,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>46014</v>
+        <v>46004</v>
       </c>
       <c r="C69" s="2">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>46014</v>
+        <v>46005</v>
       </c>
       <c r="C70" s="2">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>7</v>
@@ -1400,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>46015</v>
+        <v>46005</v>
       </c>
       <c r="C71" s="2">
-        <v>604</v>
+        <v>926</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>7</v>
@@ -1414,13 +1414,13 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>46016</v>
+        <v>46007</v>
       </c>
       <c r="C72" s="2">
-        <v>1036</v>
+        <v>33</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>46018</v>
+        <v>46007</v>
       </c>
       <c r="C73" s="2">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>7</v>
@@ -1442,10 +1442,10 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>46018</v>
+        <v>46008</v>
       </c>
       <c r="C74" s="2">
-        <v>567</v>
+        <v>334</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>7</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>46019</v>
+        <v>46010</v>
       </c>
       <c r="C75" s="2">
-        <v>1514</v>
+        <v>0</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>46020</v>
+        <v>46010</v>
       </c>
       <c r="C76" s="2">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>7</v>
@@ -1484,10 +1484,10 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>46023</v>
+        <v>46011</v>
       </c>
       <c r="C77" s="2">
-        <v>4</v>
+        <v>1001</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>7</v>
@@ -1498,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>46024</v>
+        <v>46012</v>
       </c>
       <c r="C78" s="2">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>7</v>
@@ -1512,10 +1512,10 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>46026</v>
+        <v>46013</v>
       </c>
       <c r="C79" s="2">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>7</v>
@@ -1526,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45986</v>
+        <v>46014</v>
       </c>
       <c r="C80" s="2">
-        <v>66</v>
+        <v>767</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1540,13 +1540,13 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45989</v>
+        <v>46014</v>
       </c>
       <c r="C81" s="2">
-        <v>174</v>
+        <v>1313</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,13 +1554,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>45989</v>
+        <v>46015</v>
       </c>
       <c r="C82" s="2">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,10 +1568,10 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>45990</v>
+        <v>46016</v>
       </c>
       <c r="C83" s="2">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>7</v>
@@ -1582,13 +1582,13 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>45992</v>
+        <v>46016</v>
       </c>
       <c r="C84" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c r="C85" s="2">
-        <v>55</v>
+        <v>1018</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>45993</v>
+        <v>46018</v>
       </c>
       <c r="C86" s="2">
         <v>2</v>
@@ -1624,13 +1624,13 @@
         <v>1</v>
       </c>
       <c r="B87" s="2">
-        <v>45994</v>
+        <v>46020</v>
       </c>
       <c r="C87" s="2">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1638,13 +1638,13 @@
         <v>1</v>
       </c>
       <c r="B88" s="2">
-        <v>45995</v>
+        <v>46020</v>
       </c>
       <c r="C88" s="2">
-        <v>29</v>
+        <v>2046</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1652,10 +1652,10 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>45996</v>
+        <v>46023</v>
       </c>
       <c r="C89" s="2">
-        <v>411</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>7</v>
@@ -1666,13 +1666,13 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>45996</v>
+        <v>46023</v>
       </c>
       <c r="C90" s="2">
-        <v>2</v>
+        <v>1552</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1680,13 +1680,13 @@
         <v>1</v>
       </c>
       <c r="B91" s="2">
-        <v>45997</v>
+        <v>46023</v>
       </c>
       <c r="C91" s="2">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1694,10 +1694,10 @@
         <v>1</v>
       </c>
       <c r="B92" s="2">
-        <v>45999</v>
+        <v>46023</v>
       </c>
       <c r="C92" s="2">
-        <v>358</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>7</v>
@@ -1708,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="B93" s="2">
-        <v>45999</v>
+        <v>46026</v>
       </c>
       <c r="C93" s="2">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>7</v>
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="B94" s="2">
-        <v>46000</v>
+        <v>46026</v>
       </c>
       <c r="C94" s="2">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1736,13 +1736,13 @@
         <v>1</v>
       </c>
       <c r="B95" s="2">
-        <v>46002</v>
+        <v>45974</v>
       </c>
       <c r="C95" s="2">
-        <v>321</v>
+        <v>6</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1750,13 +1750,13 @@
         <v>1</v>
       </c>
       <c r="B96" s="2">
-        <v>46003</v>
+        <v>45983</v>
       </c>
       <c r="C96" s="2">
-        <v>212</v>
+        <v>24</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1764,13 +1764,13 @@
         <v>1</v>
       </c>
       <c r="B97" s="2">
-        <v>46004</v>
+        <v>45990</v>
       </c>
       <c r="C97" s="2">
+        <v>239</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1778,10 +1778,10 @@
         <v>1</v>
       </c>
       <c r="B98" s="2">
-        <v>46007</v>
+        <v>45992</v>
       </c>
       <c r="C98" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>7</v>
@@ -1792,13 +1792,13 @@
         <v>1</v>
       </c>
       <c r="B99" s="2">
-        <v>46008</v>
+        <v>45993</v>
       </c>
       <c r="C99" s="2">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1806,13 +1806,13 @@
         <v>1</v>
       </c>
       <c r="B100" s="2">
-        <v>46011</v>
+        <v>45996</v>
       </c>
       <c r="C100" s="2">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1820,13 +1820,13 @@
         <v>1</v>
       </c>
       <c r="B101" s="2">
-        <v>46011</v>
+        <v>45999</v>
       </c>
       <c r="C101" s="2">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1834,13 +1834,13 @@
         <v>1</v>
       </c>
       <c r="B102" s="2">
-        <v>46012</v>
+        <v>46000</v>
       </c>
       <c r="C102" s="2">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1848,10 +1848,10 @@
         <v>1</v>
       </c>
       <c r="B103" s="2">
-        <v>46014</v>
+        <v>46002</v>
       </c>
       <c r="C103" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>7</v>
@@ -1862,10 +1862,10 @@
         <v>1</v>
       </c>
       <c r="B104" s="2">
-        <v>46014</v>
+        <v>46003</v>
       </c>
       <c r="C104" s="2">
-        <v>16</v>
+        <v>538</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>7</v>
@@ -1876,10 +1876,10 @@
         <v>1</v>
       </c>
       <c r="B105" s="2">
-        <v>46015</v>
+        <v>46004</v>
       </c>
       <c r="C105" s="2">
-        <v>6</v>
+        <v>132</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>7</v>
@@ -1890,13 +1890,13 @@
         <v>1</v>
       </c>
       <c r="B106" s="2">
-        <v>46015</v>
+        <v>46005</v>
       </c>
       <c r="C106" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1904,13 +1904,13 @@
         <v>1</v>
       </c>
       <c r="B107" s="2">
-        <v>46015</v>
+        <v>46005</v>
       </c>
       <c r="C107" s="2">
-        <v>311</v>
+        <v>13</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1918,13 +1918,13 @@
         <v>1</v>
       </c>
       <c r="B108" s="2">
-        <v>46016</v>
+        <v>46006</v>
       </c>
       <c r="C108" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1932,10 +1932,10 @@
         <v>1</v>
       </c>
       <c r="B109" s="2">
-        <v>46017</v>
+        <v>46006</v>
       </c>
       <c r="C109" s="2">
-        <v>1</v>
+        <v>382</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>7</v>
@@ -1946,10 +1946,10 @@
         <v>1</v>
       </c>
       <c r="B110" s="2">
-        <v>46017</v>
+        <v>46007</v>
       </c>
       <c r="C110" s="2">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>7</v>
@@ -1960,10 +1960,10 @@
         <v>1</v>
       </c>
       <c r="B111" s="2">
-        <v>46017</v>
+        <v>46008</v>
       </c>
       <c r="C111" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>7</v>
@@ -1974,10 +1974,10 @@
         <v>1</v>
       </c>
       <c r="B112" s="2">
-        <v>46018</v>
+        <v>46008</v>
       </c>
       <c r="C112" s="2">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>7</v>
@@ -1988,10 +1988,10 @@
         <v>1</v>
       </c>
       <c r="B113" s="2">
-        <v>46018</v>
+        <v>46009</v>
       </c>
       <c r="C113" s="2">
-        <v>273</v>
+        <v>49</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>5</v>
@@ -2002,10 +2002,10 @@
         <v>1</v>
       </c>
       <c r="B114" s="2">
-        <v>46019</v>
+        <v>46010</v>
       </c>
       <c r="C114" s="2">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>7</v>
@@ -2016,10 +2016,10 @@
         <v>1</v>
       </c>
       <c r="B115" s="2">
-        <v>46019</v>
+        <v>46012</v>
       </c>
       <c r="C115" s="2">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>7</v>
@@ -2030,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="B116" s="2">
-        <v>46019</v>
+        <v>46012</v>
       </c>
       <c r="C116" s="2">
-        <v>88</v>
+        <v>285</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2044,10 +2044,10 @@
         <v>1</v>
       </c>
       <c r="B117" s="2">
-        <v>46020</v>
+        <v>46013</v>
       </c>
       <c r="C117" s="2">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>7</v>
@@ -2058,10 +2058,10 @@
         <v>1</v>
       </c>
       <c r="B118" s="2">
-        <v>46020</v>
+        <v>46015</v>
       </c>
       <c r="C118" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>7</v>
@@ -2072,13 +2072,13 @@
         <v>1</v>
       </c>
       <c r="B119" s="2">
-        <v>46021</v>
+        <v>46015</v>
       </c>
       <c r="C119" s="2">
-        <v>417</v>
+        <v>3</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2086,13 +2086,13 @@
         <v>1</v>
       </c>
       <c r="B120" s="2">
-        <v>46021</v>
+        <v>46017</v>
       </c>
       <c r="C120" s="2">
-        <v>696</v>
+        <v>1</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2100,10 +2100,10 @@
         <v>1</v>
       </c>
       <c r="B121" s="2">
-        <v>46022</v>
+        <v>46018</v>
       </c>
       <c r="C121" s="2">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>7</v>
@@ -2114,13 +2114,13 @@
         <v>1</v>
       </c>
       <c r="B122" s="2">
-        <v>46022</v>
+        <v>46018</v>
       </c>
       <c r="C122" s="2">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2128,13 +2128,13 @@
         <v>1</v>
       </c>
       <c r="B123" s="2">
-        <v>46023</v>
+        <v>46019</v>
       </c>
       <c r="C123" s="2">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2142,13 +2142,13 @@
         <v>1</v>
       </c>
       <c r="B124" s="2">
-        <v>46024</v>
+        <v>46021</v>
       </c>
       <c r="C124" s="2">
-        <v>608</v>
+        <v>2</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2156,13 +2156,13 @@
         <v>1</v>
       </c>
       <c r="B125" s="2">
-        <v>46024</v>
+        <v>46021</v>
       </c>
       <c r="C125" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2170,13 +2170,13 @@
         <v>1</v>
       </c>
       <c r="B126" s="2">
-        <v>46025</v>
+        <v>46022</v>
       </c>
       <c r="C126" s="2">
-        <v>110</v>
+        <v>493</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2184,13 +2184,13 @@
         <v>1</v>
       </c>
       <c r="B127" s="2">
-        <v>46025</v>
+        <v>46022</v>
       </c>
       <c r="C127" s="2">
-        <v>1469</v>
+        <v>2030</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2198,10 +2198,10 @@
         <v>1</v>
       </c>
       <c r="B128" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C128" s="2">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>7</v>
@@ -2212,13 +2212,13 @@
         <v>1</v>
       </c>
       <c r="B129" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C129" s="2">
-        <v>906</v>
+        <v>14</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2226,7 +2226,7 @@
         <v>1</v>
       </c>
       <c r="B130" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
@@ -2240,10 +2240,10 @@
         <v>1</v>
       </c>
       <c r="B131" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C131" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>7</v>
@@ -2254,13 +2254,13 @@
         <v>1</v>
       </c>
       <c r="B132" s="2">
-        <v>45968</v>
+        <v>46025</v>
       </c>
       <c r="C132" s="2">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2268,10 +2268,10 @@
         <v>1</v>
       </c>
       <c r="B133" s="2">
-        <v>45982</v>
+        <v>46025</v>
       </c>
       <c r="C133" s="2">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>8</v>
@@ -2282,13 +2282,13 @@
         <v>1</v>
       </c>
       <c r="B134" s="2">
-        <v>45989</v>
+        <v>45983</v>
       </c>
       <c r="C134" s="2">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2296,13 +2296,13 @@
         <v>1</v>
       </c>
       <c r="B135" s="2">
-        <v>45989</v>
+        <v>45986</v>
       </c>
       <c r="C135" s="2">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2310,10 +2310,10 @@
         <v>1</v>
       </c>
       <c r="B136" s="2">
-        <v>45990</v>
+        <v>45989</v>
       </c>
       <c r="C136" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>7</v>
@@ -2324,10 +2324,10 @@
         <v>1</v>
       </c>
       <c r="B137" s="2">
-        <v>45991</v>
+        <v>45989</v>
       </c>
       <c r="C137" s="2">
-        <v>309</v>
+        <v>8</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>7</v>
@@ -2338,13 +2338,13 @@
         <v>1</v>
       </c>
       <c r="B138" s="2">
-        <v>45991</v>
+        <v>45990</v>
       </c>
       <c r="C138" s="2">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2352,10 +2352,10 @@
         <v>1</v>
       </c>
       <c r="B139" s="2">
-        <v>45992</v>
+        <v>45990</v>
       </c>
       <c r="C139" s="2">
-        <v>59</v>
+        <v>263</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>7</v>
@@ -2366,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="B140" s="2">
-        <v>45994</v>
+        <v>45991</v>
       </c>
       <c r="C140" s="2">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2380,10 +2380,10 @@
         <v>1</v>
       </c>
       <c r="B141" s="2">
-        <v>45994</v>
+        <v>45992</v>
       </c>
       <c r="C141" s="2">
-        <v>279</v>
+        <v>2</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>7</v>
@@ -2394,13 +2394,13 @@
         <v>1</v>
       </c>
       <c r="B142" s="2">
-        <v>45995</v>
+        <v>45993</v>
       </c>
       <c r="C142" s="2">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2408,10 +2408,10 @@
         <v>1</v>
       </c>
       <c r="B143" s="2">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="C143" s="2">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>7</v>
@@ -2422,13 +2422,13 @@
         <v>1</v>
       </c>
       <c r="B144" s="2">
-        <v>45997</v>
+        <v>45994</v>
       </c>
       <c r="C144" s="2">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2436,10 +2436,10 @@
         <v>1</v>
       </c>
       <c r="B145" s="2">
-        <v>45997</v>
+        <v>45995</v>
       </c>
       <c r="C145" s="2">
-        <v>1156</v>
+        <v>1</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>7</v>
@@ -2450,13 +2450,13 @@
         <v>1</v>
       </c>
       <c r="B146" s="2">
-        <v>45998</v>
+        <v>45996</v>
       </c>
       <c r="C146" s="2">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2464,13 +2464,13 @@
         <v>1</v>
       </c>
       <c r="B147" s="2">
-        <v>46000</v>
+        <v>45997</v>
       </c>
       <c r="C147" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2478,13 +2478,13 @@
         <v>1</v>
       </c>
       <c r="B148" s="2">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="C148" s="2">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2492,13 +2492,13 @@
         <v>1</v>
       </c>
       <c r="B149" s="2">
-        <v>46002</v>
+        <v>46005</v>
       </c>
       <c r="C149" s="2">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2506,13 +2506,13 @@
         <v>1</v>
       </c>
       <c r="B150" s="2">
-        <v>46003</v>
+        <v>46005</v>
       </c>
       <c r="C150" s="2">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2520,13 +2520,13 @@
         <v>1</v>
       </c>
       <c r="B151" s="2">
-        <v>46004</v>
+        <v>46006</v>
       </c>
       <c r="C151" s="2">
-        <v>248</v>
+        <v>356</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2534,13 +2534,13 @@
         <v>1</v>
       </c>
       <c r="B152" s="2">
-        <v>46005</v>
+        <v>46008</v>
       </c>
       <c r="C152" s="2">
-        <v>330</v>
+        <v>1</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2548,13 +2548,13 @@
         <v>1</v>
       </c>
       <c r="B153" s="2">
-        <v>46006</v>
+        <v>46009</v>
       </c>
       <c r="C153" s="2">
-        <v>1</v>
+        <v>489</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2562,13 +2562,13 @@
         <v>1</v>
       </c>
       <c r="B154" s="2">
-        <v>46008</v>
+        <v>46011</v>
       </c>
       <c r="C154" s="2">
-        <v>436</v>
+        <v>4</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2576,13 +2576,13 @@
         <v>1</v>
       </c>
       <c r="B155" s="2">
-        <v>46009</v>
+        <v>46012</v>
       </c>
       <c r="C155" s="2">
-        <v>2</v>
+        <v>1040</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2590,10 +2590,10 @@
         <v>1</v>
       </c>
       <c r="B156" s="2">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="C156" s="2">
-        <v>1</v>
+        <v>673</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>7</v>
@@ -2604,13 +2604,13 @@
         <v>1</v>
       </c>
       <c r="B157" s="2">
-        <v>46011</v>
+        <v>46013</v>
       </c>
       <c r="C157" s="2">
-        <v>850</v>
+        <v>3</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2618,10 +2618,10 @@
         <v>1</v>
       </c>
       <c r="B158" s="2">
-        <v>46011</v>
+        <v>46014</v>
       </c>
       <c r="C158" s="2">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>7</v>
@@ -2632,10 +2632,10 @@
         <v>1</v>
       </c>
       <c r="B159" s="2">
-        <v>46012</v>
+        <v>46014</v>
       </c>
       <c r="C159" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>1</v>
       </c>
       <c r="B160" s="2">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="C160" s="2">
-        <v>5</v>
+        <v>1186</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B161" s="2">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="C161" s="2">
-        <v>270</v>
+        <v>28</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2674,10 +2674,10 @@
         <v>1</v>
       </c>
       <c r="B162" s="2">
-        <v>46014</v>
+        <v>46016</v>
       </c>
       <c r="C162" s="2">
-        <v>39</v>
+        <v>499</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>7</v>
@@ -2688,10 +2688,10 @@
         <v>1</v>
       </c>
       <c r="B163" s="2">
-        <v>46016</v>
+        <v>46018</v>
       </c>
       <c r="C163" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>7</v>
@@ -2702,10 +2702,10 @@
         <v>1</v>
       </c>
       <c r="B164" s="2">
-        <v>46017</v>
+        <v>46018</v>
       </c>
       <c r="C164" s="2">
-        <v>723</v>
+        <v>47</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>7</v>
@@ -2716,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="B165" s="2">
-        <v>46017</v>
+        <v>46019</v>
       </c>
       <c r="C165" s="2">
-        <v>39</v>
+        <v>465</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2733,7 +2733,7 @@
         <v>46019</v>
       </c>
       <c r="C166" s="2">
-        <v>2</v>
+        <v>777</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>7</v>
@@ -2744,10 +2744,10 @@
         <v>1</v>
       </c>
       <c r="B167" s="2">
-        <v>46019</v>
+        <v>46020</v>
       </c>
       <c r="C167" s="2">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>7</v>
@@ -2758,10 +2758,10 @@
         <v>1</v>
       </c>
       <c r="B168" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C168" s="2">
-        <v>575</v>
+        <v>1</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>7</v>
@@ -2772,10 +2772,10 @@
         <v>1</v>
       </c>
       <c r="B169" s="2">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="C169" s="2">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>7</v>
@@ -2786,10 +2786,10 @@
         <v>1</v>
       </c>
       <c r="B170" s="2">
-        <v>46023</v>
+        <v>46022</v>
       </c>
       <c r="C170" s="2">
-        <v>528</v>
+        <v>607</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>5</v>
@@ -2800,10 +2800,10 @@
         <v>1</v>
       </c>
       <c r="B171" s="2">
-        <v>46023</v>
+        <v>46022</v>
       </c>
       <c r="C171" s="2">
-        <v>936</v>
+        <v>588</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>7</v>
@@ -2814,10 +2814,10 @@
         <v>1</v>
       </c>
       <c r="B172" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C172" s="2">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>7</v>
@@ -2842,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="B174" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C174" s="2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>7</v>
@@ -2856,13 +2856,13 @@
         <v>1</v>
       </c>
       <c r="B175" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C175" s="2">
-        <v>311</v>
+        <v>21</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2870,10 +2870,10 @@
         <v>1</v>
       </c>
       <c r="B176" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C176" s="2">
-        <v>969</v>
+        <v>89</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>7</v>
@@ -2884,10 +2884,10 @@
         <v>1</v>
       </c>
       <c r="B177" s="2">
-        <v>45966</v>
+        <v>46025</v>
       </c>
       <c r="C177" s="2">
-        <v>0</v>
+        <v>406</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>5</v>
@@ -2898,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="B178" s="2">
-        <v>45969</v>
+        <v>46025</v>
       </c>
       <c r="C178" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2912,13 +2912,13 @@
         <v>1</v>
       </c>
       <c r="B179" s="2">
-        <v>45985</v>
+        <v>46025</v>
       </c>
       <c r="C179" s="2">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2926,13 +2926,13 @@
         <v>1</v>
       </c>
       <c r="B180" s="2">
-        <v>45988</v>
+        <v>46026</v>
       </c>
       <c r="C180" s="2">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2940,13 +2940,13 @@
         <v>1</v>
       </c>
       <c r="B181" s="2">
-        <v>45991</v>
+        <v>45968</v>
       </c>
       <c r="C181" s="2">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2954,13 +2954,13 @@
         <v>1</v>
       </c>
       <c r="B182" s="2">
-        <v>45994</v>
+        <v>45982</v>
       </c>
       <c r="C182" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2968,10 +2968,10 @@
         <v>1</v>
       </c>
       <c r="B183" s="2">
-        <v>45996</v>
+        <v>45989</v>
       </c>
       <c r="C183" s="2">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>7</v>
@@ -2982,10 +2982,10 @@
         <v>1</v>
       </c>
       <c r="B184" s="2">
-        <v>45997</v>
+        <v>45989</v>
       </c>
       <c r="C184" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>7</v>
@@ -2996,10 +2996,10 @@
         <v>1</v>
       </c>
       <c r="B185" s="2">
-        <v>45997</v>
+        <v>45990</v>
       </c>
       <c r="C185" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>7</v>
@@ -3010,13 +3010,13 @@
         <v>1</v>
       </c>
       <c r="B186" s="2">
-        <v>45998</v>
+        <v>45991</v>
       </c>
       <c r="C186" s="2">
-        <v>85</v>
+        <v>309</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3024,13 +3024,13 @@
         <v>1</v>
       </c>
       <c r="B187" s="2">
-        <v>45998</v>
+        <v>45991</v>
       </c>
       <c r="C187" s="2">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3038,10 +3038,10 @@
         <v>1</v>
       </c>
       <c r="B188" s="2">
-        <v>45999</v>
+        <v>45992</v>
       </c>
       <c r="C188" s="2">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>7</v>
@@ -3052,10 +3052,10 @@
         <v>1</v>
       </c>
       <c r="B189" s="2">
-        <v>46001</v>
+        <v>45994</v>
       </c>
       <c r="C189" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>5</v>
@@ -3066,10 +3066,10 @@
         <v>1</v>
       </c>
       <c r="B190" s="2">
-        <v>46002</v>
+        <v>45994</v>
       </c>
       <c r="C190" s="2">
-        <v>93</v>
+        <v>279</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>7</v>
@@ -3080,10 +3080,10 @@
         <v>1</v>
       </c>
       <c r="B191" s="2">
-        <v>46004</v>
+        <v>45995</v>
       </c>
       <c r="C191" s="2">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>7</v>
@@ -3094,13 +3094,13 @@
         <v>1</v>
       </c>
       <c r="B192" s="2">
-        <v>46004</v>
+        <v>45996</v>
       </c>
       <c r="C192" s="2">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3108,13 +3108,13 @@
         <v>1</v>
       </c>
       <c r="B193" s="2">
-        <v>46005</v>
+        <v>45997</v>
       </c>
       <c r="C193" s="2">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3122,10 +3122,10 @@
         <v>1</v>
       </c>
       <c r="B194" s="2">
-        <v>46005</v>
+        <v>45997</v>
       </c>
       <c r="C194" s="2">
-        <v>926</v>
+        <v>1156</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>7</v>
@@ -3136,13 +3136,13 @@
         <v>1</v>
       </c>
       <c r="B195" s="2">
-        <v>46007</v>
+        <v>45998</v>
       </c>
       <c r="C195" s="2">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3150,13 +3150,13 @@
         <v>1</v>
       </c>
       <c r="B196" s="2">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C196" s="2">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3164,10 +3164,10 @@
         <v>1</v>
       </c>
       <c r="B197" s="2">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C197" s="2">
-        <v>334</v>
+        <v>101</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>7</v>
@@ -3178,13 +3178,13 @@
         <v>1</v>
       </c>
       <c r="B198" s="2">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C198" s="2">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3192,13 +3192,13 @@
         <v>1</v>
       </c>
       <c r="B199" s="2">
-        <v>46010</v>
+        <v>46003</v>
       </c>
       <c r="C199" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3206,13 +3206,13 @@
         <v>1</v>
       </c>
       <c r="B200" s="2">
-        <v>46011</v>
+        <v>46004</v>
       </c>
       <c r="C200" s="2">
-        <v>1001</v>
+        <v>248</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3220,13 +3220,13 @@
         <v>1</v>
       </c>
       <c r="B201" s="2">
-        <v>46012</v>
+        <v>46005</v>
       </c>
       <c r="C201" s="2">
-        <v>2</v>
+        <v>330</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3234,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="B202" s="2">
-        <v>46013</v>
+        <v>46006</v>
       </c>
       <c r="C202" s="2">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>7</v>
@@ -3248,13 +3248,13 @@
         <v>1</v>
       </c>
       <c r="B203" s="2">
-        <v>46014</v>
+        <v>46008</v>
       </c>
       <c r="C203" s="2">
-        <v>767</v>
+        <v>436</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3262,13 +3262,13 @@
         <v>1</v>
       </c>
       <c r="B204" s="2">
-        <v>46014</v>
+        <v>46009</v>
       </c>
       <c r="C204" s="2">
-        <v>1313</v>
+        <v>2</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3276,10 +3276,10 @@
         <v>1</v>
       </c>
       <c r="B205" s="2">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="C205" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>7</v>
@@ -3290,13 +3290,13 @@
         <v>1</v>
       </c>
       <c r="B206" s="2">
-        <v>46016</v>
+        <v>46011</v>
       </c>
       <c r="C206" s="2">
-        <v>1</v>
+        <v>850</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3304,10 +3304,10 @@
         <v>1</v>
       </c>
       <c r="B207" s="2">
-        <v>46016</v>
+        <v>46011</v>
       </c>
       <c r="C207" s="2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>7</v>
@@ -3318,13 +3318,13 @@
         <v>1</v>
       </c>
       <c r="B208" s="2">
-        <v>46017</v>
+        <v>46012</v>
       </c>
       <c r="C208" s="2">
-        <v>1018</v>
+        <v>4</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3332,10 +3332,10 @@
         <v>1</v>
       </c>
       <c r="B209" s="2">
-        <v>46018</v>
+        <v>46013</v>
       </c>
       <c r="C209" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>7</v>
@@ -3346,13 +3346,13 @@
         <v>1</v>
       </c>
       <c r="B210" s="2">
-        <v>46020</v>
+        <v>46013</v>
       </c>
       <c r="C210" s="2">
-        <v>5</v>
+        <v>270</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3360,13 +3360,13 @@
         <v>1</v>
       </c>
       <c r="B211" s="2">
-        <v>46020</v>
+        <v>46014</v>
       </c>
       <c r="C211" s="2">
-        <v>2046</v>
+        <v>39</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3374,10 +3374,10 @@
         <v>1</v>
       </c>
       <c r="B212" s="2">
-        <v>46023</v>
+        <v>46016</v>
       </c>
       <c r="C212" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>7</v>
@@ -3388,13 +3388,13 @@
         <v>1</v>
       </c>
       <c r="B213" s="2">
-        <v>46023</v>
+        <v>46017</v>
       </c>
       <c r="C213" s="2">
-        <v>1552</v>
+        <v>723</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3402,10 +3402,10 @@
         <v>1</v>
       </c>
       <c r="B214" s="2">
-        <v>46023</v>
+        <v>46017</v>
       </c>
       <c r="C214" s="2">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>7</v>
@@ -3416,10 +3416,10 @@
         <v>1</v>
       </c>
       <c r="B215" s="2">
-        <v>46023</v>
+        <v>46019</v>
       </c>
       <c r="C215" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>7</v>
@@ -3430,10 +3430,10 @@
         <v>1</v>
       </c>
       <c r="B216" s="2">
-        <v>46026</v>
+        <v>46019</v>
       </c>
       <c r="C216" s="2">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>7</v>
@@ -3444,10 +3444,10 @@
         <v>1</v>
       </c>
       <c r="B217" s="2">
-        <v>46026</v>
+        <v>46020</v>
       </c>
       <c r="C217" s="2">
-        <v>19</v>
+        <v>575</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>7</v>
@@ -3458,13 +3458,13 @@
         <v>1</v>
       </c>
       <c r="B218" s="2">
-        <v>45983</v>
+        <v>46020</v>
       </c>
       <c r="C218" s="2">
         <v>60</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3472,13 +3472,13 @@
         <v>1</v>
       </c>
       <c r="B219" s="2">
-        <v>45986</v>
+        <v>46023</v>
       </c>
       <c r="C219" s="2">
-        <v>61</v>
+        <v>528</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3486,10 +3486,10 @@
         <v>1</v>
       </c>
       <c r="B220" s="2">
-        <v>45989</v>
+        <v>46023</v>
       </c>
       <c r="C220" s="2">
-        <v>4</v>
+        <v>936</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>7</v>
@@ -3500,10 +3500,10 @@
         <v>1</v>
       </c>
       <c r="B221" s="2">
-        <v>45989</v>
+        <v>46024</v>
       </c>
       <c r="C221" s="2">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>7</v>
@@ -3514,13 +3514,13 @@
         <v>1</v>
       </c>
       <c r="B222" s="2">
-        <v>45990</v>
+        <v>46024</v>
       </c>
       <c r="C222" s="2">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3528,10 +3528,10 @@
         <v>1</v>
       </c>
       <c r="B223" s="2">
-        <v>45990</v>
+        <v>46025</v>
       </c>
       <c r="C223" s="2">
-        <v>263</v>
+        <v>34</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>7</v>
@@ -3542,13 +3542,13 @@
         <v>1</v>
       </c>
       <c r="B224" s="2">
-        <v>45991</v>
+        <v>46026</v>
       </c>
       <c r="C224" s="2">
-        <v>48</v>
+        <v>311</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3556,10 +3556,10 @@
         <v>1</v>
       </c>
       <c r="B225" s="2">
-        <v>45992</v>
+        <v>46026</v>
       </c>
       <c r="C225" s="2">
-        <v>2</v>
+        <v>969</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>7</v>
@@ -3570,10 +3570,10 @@
         <v>1</v>
       </c>
       <c r="B226" s="2">
-        <v>45993</v>
+        <v>45981</v>
       </c>
       <c r="C226" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>5</v>
@@ -3584,13 +3584,13 @@
         <v>1</v>
       </c>
       <c r="B227" s="2">
-        <v>45993</v>
+        <v>45984</v>
       </c>
       <c r="C227" s="2">
-        <v>183</v>
+        <v>36</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3598,13 +3598,13 @@
         <v>1</v>
       </c>
       <c r="B228" s="2">
-        <v>45994</v>
+        <v>45987</v>
       </c>
       <c r="C228" s="2">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3612,13 +3612,13 @@
         <v>1</v>
       </c>
       <c r="B229" s="2">
-        <v>45995</v>
+        <v>45989</v>
       </c>
       <c r="C229" s="2">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3626,13 +3626,13 @@
         <v>1</v>
       </c>
       <c r="B230" s="2">
-        <v>45996</v>
+        <v>45991</v>
       </c>
       <c r="C230" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3640,13 +3640,13 @@
         <v>1</v>
       </c>
       <c r="B231" s="2">
-        <v>45997</v>
+        <v>45992</v>
       </c>
       <c r="C231" s="2">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3654,13 +3654,13 @@
         <v>1</v>
       </c>
       <c r="B232" s="2">
-        <v>45999</v>
+        <v>45995</v>
       </c>
       <c r="C232" s="2">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3668,10 +3668,10 @@
         <v>1</v>
       </c>
       <c r="B233" s="2">
-        <v>46005</v>
+        <v>45996</v>
       </c>
       <c r="C233" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>7</v>
@@ -3682,10 +3682,10 @@
         <v>1</v>
       </c>
       <c r="B234" s="2">
-        <v>46005</v>
+        <v>45996</v>
       </c>
       <c r="C234" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>7</v>
@@ -3696,13 +3696,13 @@
         <v>1</v>
       </c>
       <c r="B235" s="2">
-        <v>46006</v>
+        <v>45997</v>
       </c>
       <c r="C235" s="2">
-        <v>356</v>
+        <v>62</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3710,10 +3710,10 @@
         <v>1</v>
       </c>
       <c r="B236" s="2">
-        <v>46008</v>
+        <v>45998</v>
       </c>
       <c r="C236" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>7</v>
@@ -3724,13 +3724,13 @@
         <v>1</v>
       </c>
       <c r="B237" s="2">
-        <v>46009</v>
+        <v>46003</v>
       </c>
       <c r="C237" s="2">
-        <v>489</v>
+        <v>1</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3738,10 +3738,10 @@
         <v>1</v>
       </c>
       <c r="B238" s="2">
-        <v>46011</v>
+        <v>46004</v>
       </c>
       <c r="C238" s="2">
-        <v>4</v>
+        <v>1130</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>7</v>
@@ -3752,13 +3752,13 @@
         <v>1</v>
       </c>
       <c r="B239" s="2">
-        <v>46012</v>
+        <v>46004</v>
       </c>
       <c r="C239" s="2">
-        <v>1040</v>
+        <v>10</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3766,10 +3766,10 @@
         <v>1</v>
       </c>
       <c r="B240" s="2">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C240" s="2">
-        <v>673</v>
+        <v>278</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>7</v>
@@ -3780,10 +3780,10 @@
         <v>1</v>
       </c>
       <c r="B241" s="2">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C241" s="2">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>7</v>
@@ -3794,13 +3794,13 @@
         <v>1</v>
       </c>
       <c r="B242" s="2">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C242" s="2">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3808,10 +3808,10 @@
         <v>1</v>
       </c>
       <c r="B243" s="2">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C243" s="2">
-        <v>1</v>
+        <v>555</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>7</v>
@@ -3822,13 +3822,13 @@
         <v>1</v>
       </c>
       <c r="B244" s="2">
-        <v>46015</v>
+        <v>46011</v>
       </c>
       <c r="C244" s="2">
-        <v>1186</v>
+        <v>88</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3836,10 +3836,10 @@
         <v>1</v>
       </c>
       <c r="B245" s="2">
-        <v>46015</v>
+        <v>46012</v>
       </c>
       <c r="C245" s="2">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>7</v>
@@ -3850,13 +3850,13 @@
         <v>1</v>
       </c>
       <c r="B246" s="2">
-        <v>46016</v>
+        <v>46013</v>
       </c>
       <c r="C246" s="2">
-        <v>499</v>
+        <v>348</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3864,13 +3864,13 @@
         <v>1</v>
       </c>
       <c r="B247" s="2">
-        <v>46018</v>
+        <v>46013</v>
       </c>
       <c r="C247" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3878,10 +3878,10 @@
         <v>1</v>
       </c>
       <c r="B248" s="2">
-        <v>46018</v>
+        <v>46014</v>
       </c>
       <c r="C248" s="2">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>7</v>
@@ -3892,13 +3892,13 @@
         <v>1</v>
       </c>
       <c r="B249" s="2">
-        <v>46019</v>
+        <v>46016</v>
       </c>
       <c r="C249" s="2">
-        <v>465</v>
+        <v>8</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3906,13 +3906,13 @@
         <v>1</v>
       </c>
       <c r="B250" s="2">
-        <v>46019</v>
+        <v>46016</v>
       </c>
       <c r="C250" s="2">
-        <v>777</v>
+        <v>233</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3920,10 +3920,10 @@
         <v>1</v>
       </c>
       <c r="B251" s="2">
-        <v>46020</v>
+        <v>46016</v>
       </c>
       <c r="C251" s="2">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>7</v>
@@ -3934,10 +3934,10 @@
         <v>1</v>
       </c>
       <c r="B252" s="2">
-        <v>46021</v>
+        <v>46017</v>
       </c>
       <c r="C252" s="2">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>7</v>
@@ -3948,13 +3948,13 @@
         <v>1</v>
       </c>
       <c r="B253" s="2">
-        <v>46021</v>
+        <v>46018</v>
       </c>
       <c r="C253" s="2">
-        <v>51</v>
+        <v>1017</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3962,13 +3962,13 @@
         <v>1</v>
       </c>
       <c r="B254" s="2">
-        <v>46022</v>
+        <v>46019</v>
       </c>
       <c r="C254" s="2">
-        <v>607</v>
+        <v>6</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3976,13 +3976,13 @@
         <v>1</v>
       </c>
       <c r="B255" s="2">
-        <v>46022</v>
+        <v>46019</v>
       </c>
       <c r="C255" s="2">
-        <v>588</v>
+        <v>2</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3990,10 +3990,10 @@
         <v>1</v>
       </c>
       <c r="B256" s="2">
-        <v>46023</v>
+        <v>46020</v>
       </c>
       <c r="C256" s="2">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>7</v>
@@ -4004,13 +4004,13 @@
         <v>1</v>
       </c>
       <c r="B257" s="2">
-        <v>46024</v>
+        <v>46020</v>
       </c>
       <c r="C257" s="2">
-        <v>1</v>
+        <v>486</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4018,13 +4018,13 @@
         <v>1</v>
       </c>
       <c r="B258" s="2">
-        <v>46024</v>
+        <v>46021</v>
       </c>
       <c r="C258" s="2">
-        <v>1</v>
+        <v>2287</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4032,10 +4032,10 @@
         <v>1</v>
       </c>
       <c r="B259" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C259" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>7</v>
@@ -4046,13 +4046,13 @@
         <v>1</v>
       </c>
       <c r="B260" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C260" s="2">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4060,13 +4060,13 @@
         <v>1</v>
       </c>
       <c r="B261" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C261" s="2">
-        <v>406</v>
+        <v>1456</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4077,10 +4077,10 @@
         <v>46025</v>
       </c>
       <c r="C262" s="2">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4091,7 +4091,7 @@
         <v>46025</v>
       </c>
       <c r="C263" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>7</v>
@@ -4102,10 +4102,10 @@
         <v>1</v>
       </c>
       <c r="B264" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C264" s="2">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>7</v>
@@ -4116,13 +4116,13 @@
         <v>1</v>
       </c>
       <c r="B265" s="2">
-        <v>45981</v>
+        <v>46026</v>
       </c>
       <c r="C265" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4130,13 +4130,13 @@
         <v>1</v>
       </c>
       <c r="B266" s="2">
-        <v>45984</v>
+        <v>46026</v>
       </c>
       <c r="C266" s="2">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4144,13 +4144,13 @@
         <v>1</v>
       </c>
       <c r="B267" s="2">
-        <v>45987</v>
+        <v>45984</v>
       </c>
       <c r="C267" s="2">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4158,10 +4158,10 @@
         <v>1</v>
       </c>
       <c r="B268" s="2">
-        <v>45989</v>
+        <v>45987</v>
       </c>
       <c r="C268" s="2">
-        <v>179</v>
+        <v>46</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>8</v>
@@ -4172,13 +4172,13 @@
         <v>1</v>
       </c>
       <c r="B269" s="2">
-        <v>45991</v>
+        <v>45989</v>
       </c>
       <c r="C269" s="2">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4186,10 +4186,10 @@
         <v>1</v>
       </c>
       <c r="B270" s="2">
-        <v>45992</v>
+        <v>45990</v>
       </c>
       <c r="C270" s="2">
-        <v>49</v>
+        <v>164</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>8</v>
@@ -4200,13 +4200,13 @@
         <v>1</v>
       </c>
       <c r="B271" s="2">
-        <v>45995</v>
+        <v>45991</v>
       </c>
       <c r="C271" s="2">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4214,10 +4214,10 @@
         <v>1</v>
       </c>
       <c r="B272" s="2">
-        <v>45996</v>
+        <v>45998</v>
       </c>
       <c r="C272" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>7</v>
@@ -4228,10 +4228,10 @@
         <v>1</v>
       </c>
       <c r="B273" s="2">
-        <v>45996</v>
+        <v>45998</v>
       </c>
       <c r="C273" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>7</v>
@@ -4242,13 +4242,13 @@
         <v>1</v>
       </c>
       <c r="B274" s="2">
-        <v>45997</v>
+        <v>46000</v>
       </c>
       <c r="C274" s="2">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4256,10 +4256,10 @@
         <v>1</v>
       </c>
       <c r="B275" s="2">
-        <v>45998</v>
+        <v>46001</v>
       </c>
       <c r="C275" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>7</v>
@@ -4270,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="B276" s="2">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C276" s="2">
         <v>1</v>
@@ -4284,13 +4284,13 @@
         <v>1</v>
       </c>
       <c r="B277" s="2">
-        <v>46004</v>
+        <v>46002</v>
       </c>
       <c r="C277" s="2">
-        <v>1130</v>
+        <v>45</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4298,10 +4298,10 @@
         <v>1</v>
       </c>
       <c r="B278" s="2">
-        <v>46004</v>
+        <v>46003</v>
       </c>
       <c r="C278" s="2">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>7</v>
@@ -4312,10 +4312,10 @@
         <v>1</v>
       </c>
       <c r="B279" s="2">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C279" s="2">
-        <v>278</v>
+        <v>8</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>7</v>
@@ -4326,10 +4326,10 @@
         <v>1</v>
       </c>
       <c r="B280" s="2">
-        <v>46008</v>
+        <v>46004</v>
       </c>
       <c r="C280" s="2">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>7</v>
@@ -4340,13 +4340,13 @@
         <v>1</v>
       </c>
       <c r="B281" s="2">
-        <v>46010</v>
+        <v>46005</v>
       </c>
       <c r="C281" s="2">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4354,13 +4354,13 @@
         <v>1</v>
       </c>
       <c r="B282" s="2">
-        <v>46010</v>
+        <v>46005</v>
       </c>
       <c r="C282" s="2">
-        <v>555</v>
+        <v>124</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4368,13 +4368,13 @@
         <v>1</v>
       </c>
       <c r="B283" s="2">
-        <v>46011</v>
+        <v>46005</v>
       </c>
       <c r="C283" s="2">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4382,10 +4382,10 @@
         <v>1</v>
       </c>
       <c r="B284" s="2">
-        <v>46012</v>
+        <v>46006</v>
       </c>
       <c r="C284" s="2">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>7</v>
@@ -4396,13 +4396,13 @@
         <v>1</v>
       </c>
       <c r="B285" s="2">
-        <v>46013</v>
+        <v>46006</v>
       </c>
       <c r="C285" s="2">
-        <v>348</v>
+        <v>46</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4410,13 +4410,13 @@
         <v>1</v>
       </c>
       <c r="B286" s="2">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C286" s="2">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4424,10 +4424,10 @@
         <v>1</v>
       </c>
       <c r="B287" s="2">
-        <v>46014</v>
+        <v>46009</v>
       </c>
       <c r="C287" s="2">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>7</v>
@@ -4438,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="B288" s="2">
-        <v>46016</v>
+        <v>46009</v>
       </c>
       <c r="C288" s="2">
-        <v>8</v>
+        <v>345</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>7</v>
@@ -4452,13 +4452,13 @@
         <v>1</v>
       </c>
       <c r="B289" s="2">
-        <v>46016</v>
+        <v>46009</v>
       </c>
       <c r="C289" s="2">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4466,13 +4466,13 @@
         <v>1</v>
       </c>
       <c r="B290" s="2">
-        <v>46016</v>
+        <v>46010</v>
       </c>
       <c r="C290" s="2">
-        <v>3</v>
+        <v>533</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4480,13 +4480,13 @@
         <v>1</v>
       </c>
       <c r="B291" s="2">
-        <v>46017</v>
+        <v>46011</v>
       </c>
       <c r="C291" s="2">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4494,13 +4494,13 @@
         <v>1</v>
       </c>
       <c r="B292" s="2">
-        <v>46018</v>
+        <v>46012</v>
       </c>
       <c r="C292" s="2">
-        <v>1017</v>
+        <v>883</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4508,10 +4508,10 @@
         <v>1</v>
       </c>
       <c r="B293" s="2">
-        <v>46019</v>
+        <v>46012</v>
       </c>
       <c r="C293" s="2">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>7</v>
@@ -4522,13 +4522,13 @@
         <v>1</v>
       </c>
       <c r="B294" s="2">
-        <v>46019</v>
+        <v>46013</v>
       </c>
       <c r="C294" s="2">
-        <v>2</v>
+        <v>1279</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4536,13 +4536,13 @@
         <v>1</v>
       </c>
       <c r="B295" s="2">
-        <v>46020</v>
+        <v>46014</v>
       </c>
       <c r="C295" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4550,13 +4550,13 @@
         <v>1</v>
       </c>
       <c r="B296" s="2">
-        <v>46020</v>
+        <v>46014</v>
       </c>
       <c r="C296" s="2">
-        <v>486</v>
+        <v>4</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4564,13 +4564,13 @@
         <v>1</v>
       </c>
       <c r="B297" s="2">
-        <v>46021</v>
+        <v>46015</v>
       </c>
       <c r="C297" s="2">
-        <v>2287</v>
+        <v>604</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4578,13 +4578,13 @@
         <v>1</v>
       </c>
       <c r="B298" s="2">
-        <v>46023</v>
+        <v>46016</v>
       </c>
       <c r="C298" s="2">
-        <v>1</v>
+        <v>1036</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4592,13 +4592,13 @@
         <v>1</v>
       </c>
       <c r="B299" s="2">
-        <v>46023</v>
+        <v>46018</v>
       </c>
       <c r="C299" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -4606,13 +4606,13 @@
         <v>1</v>
       </c>
       <c r="B300" s="2">
-        <v>46024</v>
+        <v>46018</v>
       </c>
       <c r="C300" s="2">
-        <v>1456</v>
+        <v>567</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4620,13 +4620,13 @@
         <v>1</v>
       </c>
       <c r="B301" s="2">
-        <v>46025</v>
+        <v>46019</v>
       </c>
       <c r="C301" s="2">
-        <v>27</v>
+        <v>1514</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4634,10 +4634,10 @@
         <v>1</v>
       </c>
       <c r="B302" s="2">
-        <v>46025</v>
+        <v>46020</v>
       </c>
       <c r="C302" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>7</v>
@@ -4648,10 +4648,10 @@
         <v>1</v>
       </c>
       <c r="B303" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C303" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>7</v>
@@ -4662,10 +4662,10 @@
         <v>1</v>
       </c>
       <c r="B304" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C304" s="2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>7</v>
@@ -4679,7 +4679,7 @@
         <v>46026</v>
       </c>
       <c r="C305" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>7</v>
@@ -4875,7 +4875,7 @@
         <v>45998</v>
       </c>
       <c r="C319" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>8</v>
